--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/82.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/82.xlsx
@@ -426,13 +426,13 @@
         <v>-9.057512038907259</v>
       </c>
       <c r="E2">
-        <v>-18.8909434908392</v>
+        <v>-17.51803244051175</v>
       </c>
       <c r="F2">
-        <v>-0.5091011241653673</v>
+        <v>0.07695004169595794</v>
       </c>
       <c r="G2">
-        <v>-14.00955452157399</v>
+        <v>-15.48357492293448</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-7.624446361382565</v>
       </c>
       <c r="E3">
-        <v>-19.49804883020352</v>
+        <v>-16.02117705659437</v>
       </c>
       <c r="F3">
-        <v>-0.7496129985724521</v>
+        <v>-0.3416289747253921</v>
       </c>
       <c r="G3">
-        <v>-12.95483457603542</v>
+        <v>-13.09094765588256</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-6.066615799112004</v>
       </c>
       <c r="E4">
-        <v>-19.29071717623633</v>
+        <v>-18.94948760281036</v>
       </c>
       <c r="F4">
-        <v>-0.008193947582855353</v>
+        <v>-0.5265860293247765</v>
       </c>
       <c r="G4">
-        <v>-12.84776160165877</v>
+        <v>-14.79661520498971</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.542486289034833</v>
       </c>
       <c r="E5">
-        <v>-20.18320694756404</v>
+        <v>-17.8339795435529</v>
       </c>
       <c r="F5">
-        <v>0.1669282932816502</v>
+        <v>-0.1505160552326945</v>
       </c>
       <c r="G5">
-        <v>-13.63756507205378</v>
+        <v>-14.5719433766943</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.045137910557052</v>
       </c>
       <c r="E6">
-        <v>-20.79409809119877</v>
+        <v>-20.09308125786339</v>
       </c>
       <c r="F6">
-        <v>0.3453398913325234</v>
+        <v>-0.770718255454556</v>
       </c>
       <c r="G6">
-        <v>-12.07218023490048</v>
+        <v>-12.96235613550065</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-1.613585171338307</v>
       </c>
       <c r="E7">
-        <v>-21.29501524355723</v>
+        <v>-19.13120167931615</v>
       </c>
       <c r="F7">
-        <v>-0.03150689051108174</v>
+        <v>-0.1594727040374622</v>
       </c>
       <c r="G7">
-        <v>-11.94049004389381</v>
+        <v>-12.91254897786231</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-0.247246545179369</v>
       </c>
       <c r="E8">
-        <v>-22.06146399782944</v>
+        <v>-22.2063208243868</v>
       </c>
       <c r="F8">
-        <v>-0.1341793368619788</v>
+        <v>-0.220600584961594</v>
       </c>
       <c r="G8">
-        <v>-13.09381127777403</v>
+        <v>-11.71130097621006</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>1.029021874587623</v>
       </c>
       <c r="E9">
-        <v>-23.42212552596614</v>
+        <v>-20.19158009600422</v>
       </c>
       <c r="F9">
-        <v>0.2480868866242601</v>
+        <v>0.2412888289822362</v>
       </c>
       <c r="G9">
-        <v>-11.33048230173662</v>
+        <v>-11.48021827647786</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>2.217372798851051</v>
       </c>
       <c r="E10">
-        <v>-22.55536654395002</v>
+        <v>-20.71975866188885</v>
       </c>
       <c r="F10">
-        <v>0.3593905302143022</v>
+        <v>0.7030024515694527</v>
       </c>
       <c r="G10">
-        <v>-10.50254465727475</v>
+        <v>-10.95463606666316</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>3.305222565048737</v>
       </c>
       <c r="E11">
-        <v>-23.83299397268207</v>
+        <v>-22.11775745821879</v>
       </c>
       <c r="F11">
-        <v>0.9459096811736397</v>
+        <v>0.4221092437304929</v>
       </c>
       <c r="G11">
-        <v>-9.637730846050939</v>
+        <v>-9.516531773858221</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>4.28299770640361</v>
       </c>
       <c r="E12">
-        <v>-23.06779507723597</v>
+        <v>-23.29734342468478</v>
       </c>
       <c r="F12">
-        <v>0.8048331582262938</v>
+        <v>0.9108575181472185</v>
       </c>
       <c r="G12">
-        <v>-10.06565527300267</v>
+        <v>-10.33406437369016</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>5.157060563777816</v>
       </c>
       <c r="E13">
-        <v>-24.92759859592012</v>
+        <v>-24.34114309803078</v>
       </c>
       <c r="F13">
-        <v>1.289748072474698</v>
+        <v>0.7441851401945402</v>
       </c>
       <c r="G13">
-        <v>-9.480665323485756</v>
+        <v>-9.752414764622371</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>5.925027940935769</v>
       </c>
       <c r="E14">
-        <v>-26.83776780251758</v>
+        <v>-25.42109357938001</v>
       </c>
       <c r="F14">
-        <v>0.9213749091316519</v>
+        <v>0.6477485358856858</v>
       </c>
       <c r="G14">
-        <v>-9.376409623363028</v>
+        <v>-9.235430041573164</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>6.590792681850998</v>
       </c>
       <c r="E15">
-        <v>-26.37436452883866</v>
+        <v>-25.68211934965613</v>
       </c>
       <c r="F15">
-        <v>1.453286296420722</v>
+        <v>1.03036713393811</v>
       </c>
       <c r="G15">
-        <v>-8.354295240840745</v>
+        <v>-8.260911372268984</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>7.171361147918991</v>
       </c>
       <c r="E16">
-        <v>-28.10758814206041</v>
+        <v>-26.66614316610088</v>
       </c>
       <c r="F16">
-        <v>1.973045908220625</v>
+        <v>1.542629481934323</v>
       </c>
       <c r="G16">
-        <v>-8.229431394736054</v>
+        <v>-8.313224612880546</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>7.674866456128344</v>
       </c>
       <c r="E17">
-        <v>-28.18516543028581</v>
+        <v>-27.39625091646154</v>
       </c>
       <c r="F17">
-        <v>1.643068111091493</v>
+        <v>1.015915817459725</v>
       </c>
       <c r="G17">
-        <v>-8.026071203349703</v>
+        <v>-7.222519037330104</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>8.109047759217356</v>
       </c>
       <c r="E18">
-        <v>-28.58280167595133</v>
+        <v>-27.38638337159882</v>
       </c>
       <c r="F18">
-        <v>1.486042085869756</v>
+        <v>1.628231954075656</v>
       </c>
       <c r="G18">
-        <v>-7.125185687929992</v>
+        <v>-7.556218717143101</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>8.483256277076125</v>
       </c>
       <c r="E19">
-        <v>-30.82555107062011</v>
+        <v>-28.83599771466819</v>
       </c>
       <c r="F19">
-        <v>1.55598962503697</v>
+        <v>1.292779285596849</v>
       </c>
       <c r="G19">
-        <v>-7.25974281137367</v>
+        <v>-8.724831360869212</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>8.79304186190773</v>
       </c>
       <c r="E20">
-        <v>-31.42460025472478</v>
+        <v>-30.67584877687454</v>
       </c>
       <c r="F20">
-        <v>1.968868092015696</v>
+        <v>2.275527403245898</v>
       </c>
       <c r="G20">
-        <v>-6.597488039515705</v>
+        <v>-8.216705657683095</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>9.03242794360259</v>
       </c>
       <c r="E21">
-        <v>-31.31244353897681</v>
+        <v>-29.45357288593824</v>
       </c>
       <c r="F21">
-        <v>1.971338673243781</v>
+        <v>2.643357355459948</v>
       </c>
       <c r="G21">
-        <v>-6.486780086136936</v>
+        <v>-6.513780895555232</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>9.198455119829671</v>
       </c>
       <c r="E22">
-        <v>-31.68751666289911</v>
+        <v>-31.05139286209364</v>
       </c>
       <c r="F22">
-        <v>1.654903145397572</v>
+        <v>1.694639910521863</v>
       </c>
       <c r="G22">
-        <v>-6.636910015797346</v>
+        <v>-5.985623081310986</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>9.277955970187362</v>
       </c>
       <c r="E23">
-        <v>-32.69730296797349</v>
+        <v>-30.9858386723586</v>
       </c>
       <c r="F23">
-        <v>1.721737118735032</v>
+        <v>2.084385185193764</v>
       </c>
       <c r="G23">
-        <v>-6.132353080702563</v>
+        <v>-6.627408750099637</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>9.26653313273046</v>
       </c>
       <c r="E24">
-        <v>-31.66716117223463</v>
+        <v>-32.08416796546796</v>
       </c>
       <c r="F24">
-        <v>2.309041787828427</v>
+        <v>1.984245876454613</v>
       </c>
       <c r="G24">
-        <v>-5.87354125153342</v>
+        <v>-6.3811074725234</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>9.165694625703651</v>
       </c>
       <c r="E25">
-        <v>-32.81725545172567</v>
+        <v>-31.57298929100812</v>
       </c>
       <c r="F25">
-        <v>2.088773634285447</v>
+        <v>2.368886866961053</v>
       </c>
       <c r="G25">
-        <v>-5.49611919678327</v>
+        <v>-6.732018678595067</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>8.970609460458688</v>
       </c>
       <c r="E26">
-        <v>-32.9073086858422</v>
+        <v>-32.60423829864186</v>
       </c>
       <c r="F26">
-        <v>2.100458216529559</v>
+        <v>1.104538416781801</v>
       </c>
       <c r="G26">
-        <v>-5.218344562765181</v>
+        <v>-5.377353375561916</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>8.690059876692223</v>
       </c>
       <c r="E27">
-        <v>-33.40403699974357</v>
+        <v>-31.89469434875003</v>
       </c>
       <c r="F27">
-        <v>1.798472421455819</v>
+        <v>1.906319626885415</v>
       </c>
       <c r="G27">
-        <v>-5.260266000928972</v>
+        <v>-5.152242899982554</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>8.335838732251663</v>
       </c>
       <c r="E28">
-        <v>-33.09841708167691</v>
+        <v>-31.02996412308935</v>
       </c>
       <c r="F28">
-        <v>2.258353696298872</v>
+        <v>1.320630337825767</v>
       </c>
       <c r="G28">
-        <v>-4.723487526100463</v>
+        <v>-4.758284670263743</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>7.915878285812653</v>
       </c>
       <c r="E29">
-        <v>-33.34299317012017</v>
+        <v>-31.28546289083911</v>
       </c>
       <c r="F29">
-        <v>1.655009253693906</v>
+        <v>1.800113140784215</v>
       </c>
       <c r="G29">
-        <v>-5.745797230809563</v>
+        <v>-5.3720664343357</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>7.451849196110174</v>
       </c>
       <c r="E30">
-        <v>-32.11346719229759</v>
+        <v>-33.14938052815923</v>
       </c>
       <c r="F30">
-        <v>1.772832222684855</v>
+        <v>1.626633994806977</v>
       </c>
       <c r="G30">
-        <v>-4.976793918037798</v>
+        <v>-5.822512502591095</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>6.960328042270492</v>
       </c>
       <c r="E31">
-        <v>-32.21052371146698</v>
+        <v>-32.03043762136695</v>
       </c>
       <c r="F31">
-        <v>1.73416287534757</v>
+        <v>1.951057735290664</v>
       </c>
       <c r="G31">
-        <v>-4.909063466849849</v>
+        <v>-5.667982857908994</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>6.453215568683965</v>
       </c>
       <c r="E32">
-        <v>-33.58192904418688</v>
+        <v>-30.89486162954451</v>
       </c>
       <c r="F32">
-        <v>1.437522087738438</v>
+        <v>2.04088870222622</v>
       </c>
       <c r="G32">
-        <v>-5.864788169127587</v>
+        <v>-6.152381881215154</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>5.953704264773076</v>
       </c>
       <c r="E33">
-        <v>-32.59336316831244</v>
+        <v>-30.44040888474175</v>
       </c>
       <c r="F33">
-        <v>1.586046779606095</v>
+        <v>1.943004590710654</v>
       </c>
       <c r="G33">
-        <v>-6.164925538263453</v>
+        <v>-4.802546664123799</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>5.469560844580783</v>
       </c>
       <c r="E34">
-        <v>-31.5725636144514</v>
+        <v>-30.02001932142469</v>
       </c>
       <c r="F34">
-        <v>1.835242905400492</v>
+        <v>1.502050185263018</v>
       </c>
       <c r="G34">
-        <v>-5.327185368459801</v>
+        <v>-6.240313281283736</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>5.006462793173343</v>
       </c>
       <c r="E35">
-        <v>-30.79707149758587</v>
+        <v>-31.47000726359969</v>
       </c>
       <c r="F35">
-        <v>2.210394330061619</v>
+        <v>1.25119116825741</v>
       </c>
       <c r="G35">
-        <v>-6.475451399301551</v>
+        <v>-7.884945957556112</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>4.57337824122783</v>
       </c>
       <c r="E36">
-        <v>-31.85242330812543</v>
+        <v>-30.39266065480487</v>
       </c>
       <c r="F36">
-        <v>1.672133865757553</v>
+        <v>2.182573368245095</v>
       </c>
       <c r="G36">
-        <v>-6.096039706682298</v>
+        <v>-7.050539507110505</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>4.163822173277035</v>
       </c>
       <c r="E37">
-        <v>-30.70683259603502</v>
+        <v>-30.02549198226296</v>
       </c>
       <c r="F37">
-        <v>2.087389475315353</v>
+        <v>1.35765104730508</v>
       </c>
       <c r="G37">
-        <v>-5.281774615297618</v>
+        <v>-6.860851868801345</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>3.774387940213569</v>
       </c>
       <c r="E38">
-        <v>-28.53438776033532</v>
+        <v>-30.63909115335428</v>
       </c>
       <c r="F38">
-        <v>1.846282919337021</v>
+        <v>1.68439333324897</v>
       </c>
       <c r="G38">
-        <v>-6.646735714957902</v>
+        <v>-7.042514744723312</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>3.400292198343389</v>
       </c>
       <c r="E39">
-        <v>-27.38808607782571</v>
+        <v>-27.80392678900206</v>
       </c>
       <c r="F39">
-        <v>1.666980486708713</v>
+        <v>2.202230326067529</v>
       </c>
       <c r="G39">
-        <v>-5.58928456934944</v>
+        <v>-5.37042771429376</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>3.027992130720123</v>
       </c>
       <c r="E40">
-        <v>-28.08540314789683</v>
+        <v>-26.73341364748482</v>
       </c>
       <c r="F40">
-        <v>1.836628648076502</v>
+        <v>1.782453236121149</v>
       </c>
       <c r="G40">
-        <v>-7.168543902857827</v>
+        <v>-6.350249877551853</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>2.652202799924019</v>
       </c>
       <c r="E41">
-        <v>-27.52003675346121</v>
+        <v>-26.87868709365089</v>
       </c>
       <c r="F41">
-        <v>1.945959785948864</v>
+        <v>1.871314975036457</v>
       </c>
       <c r="G41">
-        <v>-7.40441696198536</v>
+        <v>-8.97031162315171</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>2.266114399241848</v>
       </c>
       <c r="E42">
-        <v>-28.00721451568039</v>
+        <v>-25.25642920751309</v>
       </c>
       <c r="F42">
-        <v>2.296216937325199</v>
+        <v>1.721542322907433</v>
       </c>
       <c r="G42">
-        <v>-6.565511480151884</v>
+        <v>-7.485273726236519</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>1.858290474521811</v>
       </c>
       <c r="E43">
-        <v>-26.40642612481297</v>
+        <v>-24.4517374902461</v>
       </c>
       <c r="F43">
-        <v>2.573427237057804</v>
+        <v>2.258635595951821</v>
       </c>
       <c r="G43">
-        <v>-7.469786994203809</v>
+        <v>-8.133273289002384</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>1.429143146221645</v>
       </c>
       <c r="E44">
-        <v>-24.70329422137219</v>
+        <v>-24.6142100806933</v>
       </c>
       <c r="F44">
-        <v>1.999395607241707</v>
+        <v>1.958016539083105</v>
       </c>
       <c r="G44">
-        <v>-7.350494796241711</v>
+        <v>-7.527877136781401</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>0.977165899858999</v>
       </c>
       <c r="E45">
-        <v>-23.83758584532585</v>
+        <v>-24.28744898172183</v>
       </c>
       <c r="F45">
-        <v>2.533777575758862</v>
+        <v>1.354748114362079</v>
       </c>
       <c r="G45">
-        <v>-8.597143619419523</v>
+        <v>-8.297065840103365</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>0.4996259544940835</v>
       </c>
       <c r="E46">
-        <v>-23.53358485671693</v>
+        <v>-22.93165103466937</v>
       </c>
       <c r="F46">
-        <v>2.38244497330313</v>
+        <v>1.523373201708495</v>
       </c>
       <c r="G46">
-        <v>-8.52075609164638</v>
+        <v>-8.072587678722003</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>0.002130083934408434</v>
       </c>
       <c r="E47">
-        <v>-24.30595685499118</v>
+        <v>-23.8238011704465</v>
       </c>
       <c r="F47">
-        <v>2.097344650699805</v>
+        <v>1.604072520335627</v>
       </c>
       <c r="G47">
-        <v>-7.232139482667226</v>
+        <v>-7.778422533738983</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.5120281460106301</v>
       </c>
       <c r="E48">
-        <v>-22.76550132332795</v>
+        <v>-21.54913056249765</v>
       </c>
       <c r="F48">
-        <v>2.713884530992213</v>
+        <v>1.777746462140463</v>
       </c>
       <c r="G48">
-        <v>-8.822406380093691</v>
+        <v>-8.724920745598773</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.040248888017663</v>
       </c>
       <c r="E49">
-        <v>-22.29601178058272</v>
+        <v>-21.87994917417999</v>
       </c>
       <c r="F49">
-        <v>2.198527621637232</v>
+        <v>1.781691473575823</v>
       </c>
       <c r="G49">
-        <v>-7.66805556655076</v>
+        <v>-7.519968243488082</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-1.574258973531188</v>
       </c>
       <c r="E50">
-        <v>-21.60511155818047</v>
+        <v>-22.78198949718987</v>
       </c>
       <c r="F50">
-        <v>2.28368032129858</v>
+        <v>1.813256316176447</v>
       </c>
       <c r="G50">
-        <v>-8.026812765550501</v>
+        <v>-9.495039712217272</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.110115631705282</v>
       </c>
       <c r="E51">
-        <v>-20.34640862232647</v>
+        <v>-21.84952235732246</v>
       </c>
       <c r="F51">
-        <v>2.420004142793692</v>
+        <v>2.419630388197648</v>
       </c>
       <c r="G51">
-        <v>-8.8284514362484</v>
+        <v>-8.387317932594975</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.642275864853566</v>
       </c>
       <c r="E52">
-        <v>-20.08839881573945</v>
+        <v>-18.01890430813013</v>
       </c>
       <c r="F52">
-        <v>2.279668794214772</v>
+        <v>2.306878445547937</v>
       </c>
       <c r="G52">
-        <v>-9.423343227473275</v>
+        <v>-8.809571395037937</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.159409315331868</v>
       </c>
       <c r="E53">
-        <v>-20.27123142532514</v>
+        <v>-19.60273809231284</v>
       </c>
       <c r="F53">
-        <v>2.323819347725393</v>
+        <v>1.67990669439053</v>
       </c>
       <c r="G53">
-        <v>-9.969248876353555</v>
+        <v>-7.759820578353819</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.659688551235605</v>
       </c>
       <c r="E54">
-        <v>-18.65391863280372</v>
+        <v>-18.45736927544881</v>
       </c>
       <c r="F54">
-        <v>2.522954529532749</v>
+        <v>2.146122792895341</v>
       </c>
       <c r="G54">
-        <v>-10.34855794206109</v>
+        <v>-9.464115906334939</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.136283909568019</v>
       </c>
       <c r="E55">
-        <v>-17.9679952033359</v>
+        <v>-18.70695612038156</v>
       </c>
       <c r="F55">
-        <v>2.350731262346455</v>
+        <v>2.107059102785111</v>
       </c>
       <c r="G55">
-        <v>-10.35221278433645</v>
+        <v>-8.892043705512261</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.579933696015349</v>
       </c>
       <c r="E56">
-        <v>-16.97383213358798</v>
+        <v>-18.85904491992916</v>
       </c>
       <c r="F56">
-        <v>2.678992322263251</v>
+        <v>2.023707076749617</v>
       </c>
       <c r="G56">
-        <v>-9.765931722059214</v>
+        <v>-8.406833598548978</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.98980667359291</v>
       </c>
       <c r="E57">
-        <v>-17.33503680586179</v>
+        <v>-17.13749118422519</v>
       </c>
       <c r="F57">
-        <v>2.776334806355737</v>
+        <v>2.018509353935145</v>
       </c>
       <c r="G57">
-        <v>-10.23891267380043</v>
+        <v>-10.05402863706875</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.360085915214648</v>
       </c>
       <c r="E58">
-        <v>-16.84779111653249</v>
+        <v>-18.07247162716686</v>
       </c>
       <c r="F58">
-        <v>2.363264710961243</v>
+        <v>2.071462144923779</v>
       </c>
       <c r="G58">
-        <v>-10.82903727944875</v>
+        <v>-8.039409391327426</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.685238090431114</v>
       </c>
       <c r="E59">
-        <v>-16.21297151624123</v>
+        <v>-16.49422145143561</v>
       </c>
       <c r="F59">
-        <v>2.751301166950386</v>
+        <v>2.364013803859246</v>
       </c>
       <c r="G59">
-        <v>-11.79029059277707</v>
+        <v>-9.924331394476724</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.966243383812249</v>
       </c>
       <c r="E60">
-        <v>-15.38780656798556</v>
+        <v>-15.80462090107356</v>
       </c>
       <c r="F60">
-        <v>2.675786901490402</v>
+        <v>2.041623541770984</v>
       </c>
       <c r="G60">
-        <v>-11.17424441555626</v>
+        <v>-8.561436075232944</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.197538362528043</v>
       </c>
       <c r="E61">
-        <v>-17.29551681319685</v>
+        <v>-16.70171160199306</v>
       </c>
       <c r="F61">
-        <v>2.541045202204814</v>
+        <v>1.75798497972761</v>
       </c>
       <c r="G61">
-        <v>-11.77958759904861</v>
+        <v>-10.20762139736324</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.376660360627692</v>
       </c>
       <c r="E62">
-        <v>-16.16064047060859</v>
+        <v>-15.19620683272103</v>
       </c>
       <c r="F62">
-        <v>3.030733406082353</v>
+        <v>1.690511189200312</v>
       </c>
       <c r="G62">
-        <v>-11.91421424394861</v>
+        <v>-10.2463878856281</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.50598595661515</v>
       </c>
       <c r="E63">
-        <v>-15.70928746626409</v>
+        <v>-15.84055887079844</v>
       </c>
       <c r="F63">
-        <v>2.685298639218531</v>
+        <v>1.560230789478517</v>
       </c>
       <c r="G63">
-        <v>-11.50785802118523</v>
+        <v>-9.997414997801675</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.579350958761954</v>
       </c>
       <c r="E64">
-        <v>-15.48955685046391</v>
+        <v>-14.54596324995964</v>
       </c>
       <c r="F64">
-        <v>2.295239790775372</v>
+        <v>2.007046490519194</v>
       </c>
       <c r="G64">
-        <v>-12.27564636374408</v>
+        <v>-10.92090160761799</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.599034548429739</v>
       </c>
       <c r="E65">
-        <v>-14.64764560532787</v>
+        <v>-13.1406419111593</v>
       </c>
       <c r="F65">
-        <v>2.696839104224338</v>
+        <v>2.149648122263109</v>
       </c>
       <c r="G65">
-        <v>-12.5193157576166</v>
+        <v>-11.00191396750949</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.569083168814321</v>
       </c>
       <c r="E66">
-        <v>-15.07186399341841</v>
+        <v>-15.01099224580731</v>
       </c>
       <c r="F66">
-        <v>2.347834664227117</v>
+        <v>1.120293123228593</v>
       </c>
       <c r="G66">
-        <v>-11.7367789346803</v>
+        <v>-10.93359423921556</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.488058256592609</v>
       </c>
       <c r="E67">
-        <v>-14.80395494265063</v>
+        <v>-16.12467985851368</v>
       </c>
       <c r="F67">
-        <v>2.577576546556255</v>
+        <v>1.283118679512669</v>
       </c>
       <c r="G67">
-        <v>-12.03336739899806</v>
+        <v>-10.19977209388963</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-6.364380406186469</v>
       </c>
       <c r="E68">
-        <v>-13.67716192616606</v>
+        <v>-13.14014377901846</v>
       </c>
       <c r="F68">
-        <v>1.977142955423867</v>
+        <v>1.276969149443017</v>
       </c>
       <c r="G68">
-        <v>-12.16258792303243</v>
+        <v>-10.86181830137862</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.204881521513987</v>
       </c>
       <c r="E69">
-        <v>-15.35273353679615</v>
+        <v>-15.55213130430189</v>
       </c>
       <c r="F69">
-        <v>2.377698606674558</v>
+        <v>1.660615572634562</v>
       </c>
       <c r="G69">
-        <v>-12.98246769965172</v>
+        <v>-11.61070673945377</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.012821927327251</v>
       </c>
       <c r="E70">
-        <v>-14.54563267135708</v>
+        <v>-15.96196725894408</v>
       </c>
       <c r="F70">
-        <v>1.882614716743117</v>
+        <v>1.153246875917057</v>
       </c>
       <c r="G70">
-        <v>-12.85572346368072</v>
+        <v>-10.49972076192975</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.800609981120602</v>
       </c>
       <c r="E71">
-        <v>-14.74401606068511</v>
+        <v>-14.27136111460852</v>
       </c>
       <c r="F71">
-        <v>1.667900619845583</v>
+        <v>1.221146683335608</v>
       </c>
       <c r="G71">
-        <v>-13.04258389609934</v>
+        <v>-11.07345154606761</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.573453005659971</v>
       </c>
       <c r="E72">
-        <v>-14.79943099711697</v>
+        <v>-13.67367952965416</v>
       </c>
       <c r="F72">
-        <v>1.696247372026034</v>
+        <v>1.576373503874591</v>
       </c>
       <c r="G72">
-        <v>-12.67283568590922</v>
+        <v>-11.48473055004788</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.334835029270713</v>
       </c>
       <c r="E73">
-        <v>-14.09496346658774</v>
+        <v>-14.99673660963116</v>
       </c>
       <c r="F73">
-        <v>1.439649004782873</v>
+        <v>0.9587709569129235</v>
       </c>
       <c r="G73">
-        <v>-12.7811335621354</v>
+        <v>-11.78296435549867</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.096200896531886</v>
       </c>
       <c r="E74">
-        <v>-14.44553528189154</v>
+        <v>-13.32458399687686</v>
       </c>
       <c r="F74">
-        <v>2.153494943931711</v>
+        <v>1.333516952859698</v>
       </c>
       <c r="G74">
-        <v>-13.27774518793593</v>
+        <v>-11.58988009746622</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.857316536241695</v>
       </c>
       <c r="E75">
-        <v>-14.71752901621424</v>
+        <v>-16.97846476249783</v>
       </c>
       <c r="F75">
-        <v>1.698727455489612</v>
+        <v>0.8820182334270661</v>
       </c>
       <c r="G75">
-        <v>-12.41041205155673</v>
+        <v>-10.97457217190065</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.62144139066249</v>
       </c>
       <c r="E76">
-        <v>-14.54372618379985</v>
+        <v>-15.95694518126957</v>
       </c>
       <c r="F76">
-        <v>1.763816184908258</v>
+        <v>1.277382496686947</v>
       </c>
       <c r="G76">
-        <v>-11.68341294058724</v>
+        <v>-10.71797178715175</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.393589660381966</v>
       </c>
       <c r="E77">
-        <v>-15.92512359441767</v>
+        <v>-14.91567239641986</v>
       </c>
       <c r="F77">
-        <v>1.162739609174201</v>
+        <v>1.51445693740457</v>
       </c>
       <c r="G77">
-        <v>-12.17956771110336</v>
+        <v>-11.33497802257895</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.169297573411156</v>
       </c>
       <c r="E78">
-        <v>-15.71822667395523</v>
+        <v>-14.252753614911</v>
       </c>
       <c r="F78">
-        <v>1.548451184879478</v>
+        <v>0.8455312328412566</v>
       </c>
       <c r="G78">
-        <v>-11.01547396203835</v>
+        <v>-10.50532882607328</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.950166189045202</v>
       </c>
       <c r="E79">
-        <v>-14.62769314885008</v>
+        <v>-15.18595889604167</v>
       </c>
       <c r="F79">
-        <v>1.065463640730164</v>
+        <v>0.5368233980094338</v>
       </c>
       <c r="G79">
-        <v>-11.66135146511354</v>
+        <v>-11.55430497510121</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.734985244537188</v>
       </c>
       <c r="E80">
-        <v>-15.91225367128787</v>
+        <v>-16.48609284059184</v>
       </c>
       <c r="F80">
-        <v>1.644719916361296</v>
+        <v>0.1123688326418035</v>
       </c>
       <c r="G80">
-        <v>-11.56987778131794</v>
+        <v>-10.96731876662411</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.516787127954173</v>
       </c>
       <c r="E81">
-        <v>-16.98957310923864</v>
+        <v>-15.35574497201126</v>
       </c>
       <c r="F81">
-        <v>1.551398461588111</v>
+        <v>0.6005034210162963</v>
       </c>
       <c r="G81">
-        <v>-11.49192436550472</v>
+        <v>-11.87360047127283</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.29606663739415</v>
       </c>
       <c r="E82">
-        <v>-18.56641492955351</v>
+        <v>-16.20500593046174</v>
       </c>
       <c r="F82">
-        <v>1.692193084882509</v>
+        <v>1.031767129967359</v>
       </c>
       <c r="G82">
-        <v>-11.11832599085243</v>
+        <v>-9.255518431905463</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.068057061487719</v>
       </c>
       <c r="E83">
-        <v>-18.1514889701267</v>
+        <v>-15.81577453255445</v>
       </c>
       <c r="F83">
-        <v>1.459348722665024</v>
+        <v>0.8203107161378835</v>
       </c>
       <c r="G83">
-        <v>-11.27064750165983</v>
+        <v>-9.52298402711426</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.827122211392123</v>
       </c>
       <c r="E84">
-        <v>-20.17329864643526</v>
+        <v>-18.20197239836421</v>
       </c>
       <c r="F84">
-        <v>1.371061868997021</v>
+        <v>1.15113104481403</v>
       </c>
       <c r="G84">
-        <v>-10.7059809912085</v>
+        <v>-9.612262819217325</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.576617350185773</v>
       </c>
       <c r="E85">
-        <v>-20.09682177739372</v>
+        <v>-20.09950263400626</v>
       </c>
       <c r="F85">
-        <v>0.8706060486004095</v>
+        <v>1.64077015380819</v>
       </c>
       <c r="G85">
-        <v>-9.313294072656822</v>
+        <v>-10.69000760898152</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.314999815706102</v>
       </c>
       <c r="E86">
-        <v>-21.42288576411181</v>
+        <v>-21.3300112906885</v>
       </c>
       <c r="F86">
-        <v>1.150578331449541</v>
+        <v>1.350925048282209</v>
       </c>
       <c r="G86">
-        <v>-9.39593522095365</v>
+        <v>-8.981130485974049</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.04551610817823</v>
       </c>
       <c r="E87">
-        <v>-22.89171895086973</v>
+        <v>-23.5362204285894</v>
       </c>
       <c r="F87">
-        <v>1.298192392415821</v>
+        <v>0.9177624759385344</v>
       </c>
       <c r="G87">
-        <v>-9.365564276176375</v>
+        <v>-8.573450044994958</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-1.775661157134119</v>
       </c>
       <c r="E88">
-        <v>-23.10095256392013</v>
+        <v>-21.97930842238229</v>
       </c>
       <c r="F88">
-        <v>1.273165087834132</v>
+        <v>0.1114653284170453</v>
       </c>
       <c r="G88">
-        <v>-8.644553942087425</v>
+        <v>-8.197905069565575</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-1.510011045968199</v>
       </c>
       <c r="E89">
-        <v>-24.75083414150471</v>
+        <v>-23.70750542945552</v>
       </c>
       <c r="F89">
-        <v>0.85224614592272</v>
+        <v>0.5770265645258219</v>
       </c>
       <c r="G89">
-        <v>-8.985103140621174</v>
+        <v>-8.469777000887142</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.259110534078655</v>
       </c>
       <c r="E90">
-        <v>-26.203351236413</v>
+        <v>-25.77392510321363</v>
       </c>
       <c r="F90">
-        <v>1.128598077049157</v>
+        <v>0.195994839800668</v>
       </c>
       <c r="G90">
-        <v>-8.857100897345253</v>
+        <v>-8.429252612940923</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.032353768826619</v>
       </c>
       <c r="E91">
-        <v>-26.85739420886682</v>
+        <v>-25.76821469748996</v>
       </c>
       <c r="F91">
-        <v>0.6064359833755324</v>
+        <v>0.1918661184791174</v>
       </c>
       <c r="G91">
-        <v>-8.724622796500238</v>
+        <v>-8.952040722320472</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.8357510408408689</v>
       </c>
       <c r="E92">
-        <v>-28.93789290831478</v>
+        <v>-30.06741885886298</v>
       </c>
       <c r="F92">
-        <v>0.6738369234307199</v>
+        <v>0.1488170324326846</v>
       </c>
       <c r="G92">
-        <v>-8.716856256665109</v>
+        <v>-8.904445009102371</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-0.6784735060779169</v>
       </c>
       <c r="E93">
-        <v>-30.28196210768737</v>
+        <v>-30.70766809948944</v>
       </c>
       <c r="F93">
-        <v>0.5397857199242633</v>
+        <v>-0.1201041505385107</v>
       </c>
       <c r="G93">
-        <v>-8.981435056163662</v>
+        <v>-8.094708744015414</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-0.5626250320856824</v>
       </c>
       <c r="E94">
-        <v>-30.92251022759834</v>
+        <v>-33.64029428143474</v>
       </c>
       <c r="F94">
-        <v>0.004227849764893953</v>
+        <v>0.1308791873814597</v>
       </c>
       <c r="G94">
-        <v>-8.64689118723815</v>
+        <v>-8.751309104092304</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-0.4866063034503886</v>
       </c>
       <c r="E95">
-        <v>-32.79052160542139</v>
+        <v>-32.87187111249518</v>
       </c>
       <c r="F95">
-        <v>-0.01925692525515761</v>
+        <v>-0.2430702044898489</v>
       </c>
       <c r="G95">
-        <v>-7.736342189389307</v>
+        <v>-8.099972511422854</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-0.4481066488164871</v>
       </c>
       <c r="E96">
-        <v>-34.82604576526217</v>
+        <v>-35.80915482995736</v>
       </c>
       <c r="F96">
-        <v>-0.003704933165542239</v>
+        <v>-0.2203622372213204</v>
       </c>
       <c r="G96">
-        <v>-7.555401012394901</v>
+        <v>-7.193392857675597</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-0.4373074328185106</v>
       </c>
       <c r="E97">
-        <v>-38.1156379678101</v>
+        <v>-37.44612572814608</v>
       </c>
       <c r="F97">
-        <v>-0.3515271366968886</v>
+        <v>-0.1097775961168878</v>
       </c>
       <c r="G97">
-        <v>-8.683555479085578</v>
+        <v>-7.521524199891539</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-0.4447318881619389</v>
       </c>
       <c r="E98">
-        <v>-39.21480050013687</v>
+        <v>-39.6768542885615</v>
       </c>
       <c r="F98">
-        <v>-0.5833317959808874</v>
+        <v>-0.6036309465520325</v>
       </c>
       <c r="G98">
-        <v>-8.203436991161697</v>
+        <v>-8.716703971570301</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-0.4583084310737016</v>
       </c>
       <c r="E99">
-        <v>-40.95246428212314</v>
+        <v>-42.00512617910214</v>
       </c>
       <c r="F99">
-        <v>-0.621598090162693</v>
+        <v>-0.6253554324470731</v>
       </c>
       <c r="G99">
-        <v>-7.990016051881501</v>
+        <v>-8.789645221437063</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-0.4677497269764263</v>
       </c>
       <c r="E100">
-        <v>-44.14592150996224</v>
+        <v>-44.10311384516773</v>
       </c>
       <c r="F100">
-        <v>-1.101065056061986</v>
+        <v>-0.9553585688708525</v>
       </c>
       <c r="G100">
-        <v>-8.873716525406856</v>
+        <v>-8.937550464495082</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-0.461160032353676</v>
       </c>
       <c r="E101">
-        <v>-45.16746826203454</v>
+        <v>-46.49602743793086</v>
       </c>
       <c r="F101">
-        <v>-1.097919024260965</v>
+        <v>-1.008275726476388</v>
       </c>
       <c r="G101">
-        <v>-7.942546139393891</v>
+        <v>-9.35691382068226</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-0.4370445040674777</v>
       </c>
       <c r="E102">
-        <v>-46.74662186833032</v>
+        <v>-47.13881035976461</v>
       </c>
       <c r="F102">
-        <v>-0.8800383073855101</v>
+        <v>-1.104447060044407</v>
       </c>
       <c r="G102">
-        <v>-8.765292848450185</v>
+        <v>-9.142933399205928</v>
       </c>
     </row>
   </sheetData>
